--- a/outputs/homophobie/homophobie_annotations_gold_flat.xlsx
+++ b/outputs/homophobie/homophobie_annotations_gold_flat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV104"/>
+  <dimension ref="A1:AX104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,6 +657,16 @@
           <t>Complexe</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>typo</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>elongation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -821,6 +831,12 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -965,6 +981,12 @@
       <c r="AV3" t="n">
         <v>0</v>
       </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1131,6 +1153,12 @@
       <c r="AV4" t="n">
         <v>0</v>
       </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1297,6 +1325,12 @@
       <c r="AV5" t="n">
         <v>0</v>
       </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1475,6 +1509,12 @@
       <c r="AV6" t="n">
         <v>0</v>
       </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1639,6 +1679,12 @@
         <v>1</v>
       </c>
       <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1783,6 +1829,12 @@
       <c r="AV8" t="n">
         <v>0</v>
       </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1947,6 +1999,12 @@
         <v>1</v>
       </c>
       <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2091,6 +2149,12 @@
       <c r="AV10" t="n">
         <v>0</v>
       </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2233,6 +2297,12 @@
       <c r="AV11" t="n">
         <v>0</v>
       </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2387,6 +2457,12 @@
       <c r="AV12" t="n">
         <v>0</v>
       </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2541,6 +2617,12 @@
       <c r="AV13" t="n">
         <v>0</v>
       </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2707,6 +2789,12 @@
       <c r="AV14" t="n">
         <v>0</v>
       </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2859,6 +2947,12 @@
         <v>1</v>
       </c>
       <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3015,6 +3109,12 @@
       <c r="AV16" t="n">
         <v>0</v>
       </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3167,6 +3267,12 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3311,6 +3417,12 @@
       <c r="AV18" t="n">
         <v>0</v>
       </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3457,6 +3569,12 @@
       <c r="AV19" t="n">
         <v>0</v>
       </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3599,6 +3717,12 @@
       <c r="AV20" t="n">
         <v>0</v>
       </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3741,6 +3865,12 @@
       <c r="AV21" t="n">
         <v>0</v>
       </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3881,6 +4011,12 @@
         <v>0</v>
       </c>
       <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4025,6 +4161,12 @@
       <c r="AV23" t="n">
         <v>0</v>
       </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4205,6 +4347,12 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4349,6 +4497,12 @@
       <c r="AV25" t="n">
         <v>0</v>
       </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4491,6 +4645,12 @@
       <c r="AV26" t="n">
         <v>0</v>
       </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4633,6 +4793,12 @@
       <c r="AV27" t="n">
         <v>0</v>
       </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4773,6 +4939,12 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4917,6 +5089,12 @@
       <c r="AV29" t="n">
         <v>0</v>
       </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5059,6 +5237,12 @@
       <c r="AV30" t="n">
         <v>0</v>
       </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5201,6 +5385,12 @@
       <c r="AV31" t="n">
         <v>0</v>
       </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5343,6 +5533,12 @@
       <c r="AV32" t="n">
         <v>0</v>
       </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5483,6 +5679,12 @@
         <v>1</v>
       </c>
       <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5627,6 +5829,12 @@
       <c r="AV34" t="n">
         <v>0</v>
       </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5779,6 +5987,12 @@
         <v>1</v>
       </c>
       <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5923,6 +6137,12 @@
       <c r="AV36" t="n">
         <v>0</v>
       </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6065,6 +6285,12 @@
       <c r="AV37" t="n">
         <v>0</v>
       </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6207,6 +6433,12 @@
       <c r="AV38" t="n">
         <v>0</v>
       </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6349,6 +6581,12 @@
       <c r="AV39" t="n">
         <v>0</v>
       </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6501,6 +6739,12 @@
         <v>1</v>
       </c>
       <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6645,6 +6889,12 @@
       <c r="AV41" t="n">
         <v>0</v>
       </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6787,6 +7037,12 @@
       <c r="AV42" t="n">
         <v>0</v>
       </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6939,6 +7195,12 @@
         <v>1</v>
       </c>
       <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7087,6 +7349,12 @@
       <c r="AV44" t="n">
         <v>0</v>
       </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7229,6 +7497,12 @@
       <c r="AV45" t="n">
         <v>0</v>
       </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7383,6 +7657,12 @@
       <c r="AV46" t="n">
         <v>0</v>
       </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7535,6 +7815,12 @@
         <v>1</v>
       </c>
       <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7679,6 +7965,12 @@
       <c r="AV48" t="n">
         <v>0</v>
       </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7821,6 +8113,12 @@
       <c r="AV49" t="n">
         <v>0</v>
       </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7985,6 +8283,12 @@
         <v>1</v>
       </c>
       <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8129,6 +8433,12 @@
       <c r="AV51" t="n">
         <v>0</v>
       </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8281,6 +8591,12 @@
         <v>1</v>
       </c>
       <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8429,6 +8745,12 @@
       <c r="AV53" t="n">
         <v>0</v>
       </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8571,6 +8893,12 @@
       <c r="AV54" t="n">
         <v>0</v>
       </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8723,6 +9051,12 @@
         <v>1</v>
       </c>
       <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8867,6 +9201,12 @@
       <c r="AV56" t="n">
         <v>0</v>
       </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -9009,6 +9349,12 @@
       <c r="AV57" t="n">
         <v>0</v>
       </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9149,6 +9495,12 @@
         <v>0</v>
       </c>
       <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9293,6 +9645,12 @@
       <c r="AV59" t="n">
         <v>0</v>
       </c>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9435,6 +9793,12 @@
       <c r="AV60" t="n">
         <v>0</v>
       </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9577,6 +9941,12 @@
       <c r="AV61" t="n">
         <v>0</v>
       </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9741,6 +10111,12 @@
         <v>1</v>
       </c>
       <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9885,6 +10261,12 @@
       <c r="AV63" t="n">
         <v>0</v>
       </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -10027,6 +10409,12 @@
       <c r="AV64" t="n">
         <v>0</v>
       </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -10169,6 +10557,12 @@
       <c r="AV65" t="n">
         <v>0</v>
       </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -10311,6 +10705,12 @@
       <c r="AV66" t="n">
         <v>0</v>
       </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10453,6 +10853,12 @@
       <c r="AV67" t="n">
         <v>0</v>
       </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10595,6 +11001,12 @@
       <c r="AV68" t="n">
         <v>0</v>
       </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10747,6 +11159,12 @@
         <v>1</v>
       </c>
       <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10891,6 +11309,12 @@
       <c r="AV70" t="n">
         <v>0</v>
       </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -11033,6 +11457,12 @@
       <c r="AV71" t="n">
         <v>0</v>
       </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -11185,6 +11615,12 @@
         <v>1</v>
       </c>
       <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11329,6 +11765,12 @@
       <c r="AV73" t="n">
         <v>0</v>
       </c>
+      <c r="AW73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11471,6 +11913,12 @@
       <c r="AV74" t="n">
         <v>0</v>
       </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11617,6 +12065,12 @@
       <c r="AV75" t="n">
         <v>0</v>
       </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11763,6 +12217,12 @@
       <c r="AV76" t="n">
         <v>0</v>
       </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11905,6 +12365,12 @@
       <c r="AV77" t="n">
         <v>0</v>
       </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -12047,6 +12513,12 @@
       <c r="AV78" t="n">
         <v>0</v>
       </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12199,6 +12671,12 @@
         <v>1</v>
       </c>
       <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12347,6 +12825,12 @@
       <c r="AV80" t="n">
         <v>0</v>
       </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12499,6 +12983,12 @@
         <v>1</v>
       </c>
       <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12643,6 +13133,12 @@
       <c r="AV82" t="n">
         <v>0</v>
       </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12795,6 +13291,12 @@
         <v>1</v>
       </c>
       <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12939,6 +13441,12 @@
       <c r="AV84" t="n">
         <v>0</v>
       </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -13117,6 +13625,12 @@
       <c r="AV85" t="n">
         <v>0</v>
       </c>
+      <c r="AW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -13293,6 +13807,12 @@
         <v>1</v>
       </c>
       <c r="AV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13435,6 +13955,12 @@
         <v>0</v>
       </c>
       <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13579,6 +14105,12 @@
       <c r="AV88" t="n">
         <v>0</v>
       </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13721,6 +14253,12 @@
       <c r="AV89" t="n">
         <v>0</v>
       </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13863,6 +14401,12 @@
       <c r="AV90" t="n">
         <v>0</v>
       </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -14017,6 +14561,12 @@
       <c r="AV91" t="n">
         <v>0</v>
       </c>
+      <c r="AW91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -14181,6 +14731,12 @@
         <v>1</v>
       </c>
       <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14325,6 +14881,12 @@
       <c r="AV93" t="n">
         <v>0</v>
       </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -14479,6 +15041,12 @@
       <c r="AV94" t="n">
         <v>0</v>
       </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -14645,6 +15213,12 @@
       <c r="AV95" t="n">
         <v>0</v>
       </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -14835,6 +15409,12 @@
       <c r="AV96" t="n">
         <v>0</v>
       </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -15011,6 +15591,12 @@
         <v>1</v>
       </c>
       <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15155,6 +15741,12 @@
       <c r="AV98" t="n">
         <v>0</v>
       </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -15297,6 +15889,12 @@
       <c r="AV99" t="n">
         <v>0</v>
       </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -15439,6 +16037,12 @@
       <c r="AV100" t="n">
         <v>0</v>
       </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -15581,6 +16185,12 @@
       <c r="AV101" t="n">
         <v>0</v>
       </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -15723,6 +16333,12 @@
       <c r="AV102" t="n">
         <v>0</v>
       </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -15865,6 +16481,12 @@
       <c r="AV103" t="n">
         <v>0</v>
       </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -16029,6 +16651,12 @@
         <v>1</v>
       </c>
       <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
         <v>0</v>
       </c>
     </row>

--- a/outputs/homophobie/homophobie_annotations_gold_flat.xlsx
+++ b/outputs/homophobie/homophobie_annotations_gold_flat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX104"/>
+  <dimension ref="A1:BE104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,41 @@
           <t>elongation</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>ironie</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>insulte</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>emoji</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>mépris / haine</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>argot</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>abréviation</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>interjection</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -764,7 +799,6 @@
       <c r="Y2" t="b">
         <v>1</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>2</v>
       </c>
@@ -783,8 +817,6 @@
           <t>bande de salopes</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -795,8 +827,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -807,8 +837,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
@@ -837,6 +865,27 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -936,7 +985,6 @@
       <c r="Y3" t="b">
         <v>1</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
@@ -945,18 +993,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
@@ -985,6 +1021,27 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1084,7 +1141,6 @@
       <c r="Y4" t="b">
         <v>1</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>2</v>
       </c>
@@ -1103,8 +1159,6 @@
           <t>sa dégouteeee</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -1115,8 +1169,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
           <t>Désignée</t>
@@ -1127,8 +1179,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
@@ -1157,6 +1207,27 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1256,7 +1327,6 @@
       <c r="Y5" t="b">
         <v>1</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>2</v>
       </c>
@@ -1275,8 +1345,6 @@
           <t>je vois pas en quoi ça te concerne</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -1287,8 +1355,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -1299,8 +1365,6 @@
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
@@ -1329,6 +1393,27 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1428,7 +1513,6 @@
       <c r="Y6" t="b">
         <v>1</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>3</v>
       </c>
@@ -1452,7 +1536,6 @@
           <t>aaaaah</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -1468,7 +1551,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -1484,7 +1566,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
@@ -1514,6 +1595,27 @@
       </c>
       <c r="AX6" t="n">
         <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1612,7 +1714,6 @@
       <c r="Y7" t="b">
         <v>1</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>2</v>
       </c>
@@ -1631,8 +1732,6 @@
           <t>tu dégoute</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -1643,8 +1742,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -1655,8 +1752,6 @@
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
@@ -1686,6 +1781,27 @@
       </c>
       <c r="AX7" t="n">
         <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1784,7 +1900,6 @@
       <c r="Y8" t="b">
         <v>1</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
@@ -1793,18 +1908,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
@@ -1833,6 +1936,27 @@
         <v>0</v>
       </c>
       <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1932,7 +2056,6 @@
       <c r="Y9" t="b">
         <v>1</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
@@ -1951,8 +2074,6 @@
           <t>bande de crasseuse</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -1963,8 +2084,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
           <t>Désignée</t>
@@ -1975,8 +2094,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
@@ -2005,6 +2122,27 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2104,7 +2242,6 @@
       <c r="Y10" t="b">
         <v>1</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
@@ -2113,18 +2250,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
@@ -2153,6 +2278,27 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2252,7 +2398,6 @@
       <c r="Y11" t="b">
         <v>1</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
@@ -2261,18 +2406,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
@@ -2301,6 +2434,27 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2400,7 +2554,6 @@
       <c r="Y12" t="b">
         <v>1</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
         <v>1</v>
       </c>
@@ -2414,25 +2567,16 @@
           <t>grosse crasseuse</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
@@ -2461,6 +2605,27 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2560,7 +2725,6 @@
       <c r="Y13" t="b">
         <v>1</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
         <v>1</v>
       </c>
@@ -2574,25 +2738,16 @@
           <t>vous me degoutez</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
@@ -2621,6 +2776,27 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2720,7 +2896,6 @@
       <c r="Y14" t="b">
         <v>1</v>
       </c>
-      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
         <v>2</v>
       </c>
@@ -2739,8 +2914,6 @@
           <t>laissez nous tranquille</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -2751,8 +2924,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -2763,8 +2934,6 @@
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
@@ -2794,6 +2963,27 @@
       </c>
       <c r="AX14" t="n">
         <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2892,7 +3082,6 @@
       <c r="Y15" t="b">
         <v>1</v>
       </c>
-      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>1</v>
       </c>
@@ -2906,25 +3095,16 @@
           <t>grosse pute</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
         <v>1</v>
       </c>
@@ -2953,6 +3133,27 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,7 +3253,6 @@
       <c r="Y16" t="b">
         <v>1</v>
       </c>
-      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
         <v>1</v>
       </c>
@@ -3066,25 +3266,16 @@
           <t>sal photo</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
         <v>2</v>
       </c>
@@ -3113,6 +3304,27 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3212,7 +3424,6 @@
       <c r="Y17" t="b">
         <v>1</v>
       </c>
-      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
         <v>1</v>
       </c>
@@ -3226,25 +3437,16 @@
           <t>connasses</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
@@ -3273,6 +3475,27 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3372,7 +3595,6 @@
       <c r="Y18" t="b">
         <v>1</v>
       </c>
-      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
@@ -3381,18 +3603,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
         <v>1</v>
       </c>
@@ -3421,6 +3631,27 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3533,18 +3764,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
@@ -3573,6 +3792,27 @@
         <v>0</v>
       </c>
       <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3672,7 +3912,6 @@
       <c r="Y20" t="b">
         <v>0</v>
       </c>
-      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
@@ -3681,18 +3920,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
@@ -3721,6 +3948,27 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3820,7 +4068,6 @@
       <c r="Y21" t="b">
         <v>1</v>
       </c>
-      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
         <v>0</v>
       </c>
@@ -3829,18 +4076,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
@@ -3869,6 +4104,27 @@
         <v>0</v>
       </c>
       <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3968,7 +4224,6 @@
       <c r="Y22" t="b">
         <v>1</v>
       </c>
-      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
@@ -3977,18 +4232,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="n">
         <v>1</v>
       </c>
@@ -4017,6 +4260,27 @@
         <v>0</v>
       </c>
       <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4116,7 +4380,6 @@
       <c r="Y23" t="b">
         <v>1</v>
       </c>
-      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
         <v>0</v>
       </c>
@@ -4125,18 +4388,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="n">
         <v>2</v>
       </c>
@@ -4165,6 +4416,27 @@
         <v>0</v>
       </c>
       <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4292,7 +4564,6 @@
           <t>je lui tenais la main pour la réconforter</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -4308,7 +4579,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -4324,7 +4594,6 @@
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
@@ -4353,6 +4622,27 @@
         <v>0</v>
       </c>
       <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4452,7 +4742,6 @@
       <c r="Y25" t="b">
         <v>1</v>
       </c>
-      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
         <v>0</v>
       </c>
@@ -4461,18 +4750,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="n">
         <v>2</v>
       </c>
@@ -4501,6 +4778,27 @@
         <v>0</v>
       </c>
       <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4600,7 +4898,6 @@
       <c r="Y26" t="b">
         <v>1</v>
       </c>
-      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
         <v>0</v>
       </c>
@@ -4609,18 +4906,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="n">
         <v>2</v>
       </c>
@@ -4649,6 +4934,27 @@
         <v>0</v>
       </c>
       <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4748,7 +5054,6 @@
       <c r="Y27" t="b">
         <v>1</v>
       </c>
-      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
@@ -4757,18 +5062,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="n">
         <v>1</v>
       </c>
@@ -4797,6 +5090,27 @@
         <v>0</v>
       </c>
       <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4896,7 +5210,6 @@
       <c r="Y28" t="b">
         <v>1</v>
       </c>
-      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
         <v>0</v>
       </c>
@@ -4905,18 +5218,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="n">
         <v>1</v>
       </c>
@@ -4945,6 +5246,27 @@
         <v>0</v>
       </c>
       <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5044,7 +5366,6 @@
       <c r="Y29" t="b">
         <v>1</v>
       </c>
-      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
         <v>0</v>
       </c>
@@ -5053,18 +5374,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="n">
         <v>2</v>
       </c>
@@ -5093,6 +5402,27 @@
         <v>0</v>
       </c>
       <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5192,7 +5522,6 @@
       <c r="Y30" t="b">
         <v>1</v>
       </c>
-      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
@@ -5201,18 +5530,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="n">
         <v>2</v>
       </c>
@@ -5241,6 +5558,27 @@
         <v>0</v>
       </c>
       <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5340,7 +5678,6 @@
       <c r="Y31" t="b">
         <v>0</v>
       </c>
-      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
         <v>2</v>
       </c>
@@ -5349,18 +5686,6 @@
           <t>[{"span_text": "burk", "mode": "Montrée", "categorie": "Dégoût", "categorie2": null, "justification": "Interjection exprimant directement le dégoût de manière formelle/exclamative."}, {"span_text": "sa me degoute", "mode": "Désignée", "categorie": "Dégoût", "categorie2": null, "justification": "Le terme 'degoute' est un mot du lexique émotionnel nommant explicitement l'émotion ressentie."}]</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
@@ -5390,6 +5715,27 @@
       </c>
       <c r="AX31" t="n">
         <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -5488,7 +5834,6 @@
       <c r="Y32" t="b">
         <v>0</v>
       </c>
-      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
         <v>1</v>
       </c>
@@ -5497,18 +5842,6 @@
           <t>[{"span_text": "mellez-vous de votre cul", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'expression vulgaire et impérative 'mellez-vous de votre cul' est une insulte/injonction à forte charge affective négative qui exprime l'indignation et la colère de la victime face aux attaques."}]</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
@@ -5537,6 +5870,27 @@
         <v>0</v>
       </c>
       <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5636,7 +5990,6 @@
       <c r="Y33" t="b">
         <v>0</v>
       </c>
-      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
         <v>1</v>
       </c>
@@ -5645,18 +5998,6 @@
           <t>[{"span_text": "connasse", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "Insulte à forte charge affective péjorative qui exprime la colère et le mépris de l'auteur envers la victime."}]</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
@@ -5685,6 +6026,27 @@
         <v>0</v>
       </c>
       <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5784,7 +6146,6 @@
       <c r="Y34" t="b">
         <v>1</v>
       </c>
-      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
         <v>0</v>
       </c>
@@ -5793,18 +6154,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="n">
         <v>2</v>
       </c>
@@ -5833,6 +6182,27 @@
         <v>0</v>
       </c>
       <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5932,7 +6302,6 @@
       <c r="Y35" t="b">
         <v>1</v>
       </c>
-      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
         <v>1</v>
       </c>
@@ -5946,25 +6315,16 @@
           <t>cul de crasseuse</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
@@ -5993,6 +6353,27 @@
         <v>0</v>
       </c>
       <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6092,7 +6473,6 @@
       <c r="Y36" t="b">
         <v>1</v>
       </c>
-      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="n">
         <v>0</v>
       </c>
@@ -6101,18 +6481,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="n">
         <v>1</v>
       </c>
@@ -6141,6 +6509,27 @@
         <v>0</v>
       </c>
       <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6240,7 +6629,6 @@
       <c r="Y37" t="b">
         <v>0</v>
       </c>
-      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
         <v>2</v>
       </c>
@@ -6249,18 +6637,6 @@
           <t>[{"span_text": "tg", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'abréviation 'tg' (tais-toi/ferme ta gueule) est un marqueur discursif agressif exprimant la colère de l'auteur."}, {"span_text": "saloppe", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'insulte 'saloppe' est un terme péjoratif à forte charge affective négative exprimant la colère de l'auteur."}]</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
@@ -6289,6 +6665,27 @@
         <v>1</v>
       </c>
       <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6388,7 +6785,6 @@
       <c r="Y38" t="b">
         <v>0</v>
       </c>
-      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
         <v>1</v>
       </c>
@@ -6397,18 +6793,6 @@
           <t>[{"span_text": "tg", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'abréviation 'tg' (tais-toi/ferme ta gueule) est un marqueur d'hostilité et d'agression verbale exprimant de la colère."}]</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
@@ -6437,6 +6821,27 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6536,7 +6941,6 @@
       <c r="Y39" t="b">
         <v>1</v>
       </c>
-      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="n">
         <v>0</v>
       </c>
@@ -6545,18 +6949,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="n">
         <v>1</v>
       </c>
@@ -6585,6 +6977,27 @@
         <v>0</v>
       </c>
       <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6684,7 +7097,6 @@
       <c r="Y40" t="b">
         <v>1</v>
       </c>
-      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
@@ -6698,25 +7110,16 @@
           <t>saloperie</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="n">
         <v>1</v>
       </c>
@@ -6745,6 +7148,27 @@
         <v>0</v>
       </c>
       <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6844,7 +7268,6 @@
       <c r="Y41" t="b">
         <v>1</v>
       </c>
-      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
         <v>0</v>
       </c>
@@ -6853,18 +7276,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="n">
         <v>1</v>
       </c>
@@ -6893,6 +7304,27 @@
         <v>0</v>
       </c>
       <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6992,7 +7424,6 @@
       <c r="Y42" t="b">
         <v>1</v>
       </c>
-      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="n">
         <v>0</v>
       </c>
@@ -7001,18 +7432,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="n">
         <v>1</v>
       </c>
@@ -7041,6 +7460,27 @@
         <v>0</v>
       </c>
       <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7140,7 +7580,6 @@
       <c r="Y43" t="b">
         <v>1</v>
       </c>
-      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="n">
         <v>1</v>
       </c>
@@ -7154,25 +7593,16 @@
           <t>grosse crasseuse</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
@@ -7201,6 +7631,27 @@
         <v>0</v>
       </c>
       <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7313,18 +7764,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="n">
         <v>1</v>
       </c>
@@ -7353,6 +7792,27 @@
         <v>0</v>
       </c>
       <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7452,7 +7912,6 @@
       <c r="Y45" t="b">
         <v>1</v>
       </c>
-      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
@@ -7461,18 +7920,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="n">
         <v>1</v>
       </c>
@@ -7501,6 +7948,27 @@
         <v>0</v>
       </c>
       <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7600,7 +8068,6 @@
       <c r="Y46" t="b">
         <v>1</v>
       </c>
-      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="n">
         <v>1</v>
       </c>
@@ -7614,25 +8081,16 @@
           <t>on veut pas de sa ici</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
@@ -7661,6 +8119,27 @@
         <v>0</v>
       </c>
       <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7760,7 +8239,6 @@
       <c r="Y47" t="b">
         <v>1</v>
       </c>
-      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="n">
         <v>1</v>
       </c>
@@ -7774,25 +8252,16 @@
           <t>crasseuse</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
@@ -7821,6 +8290,27 @@
         <v>0</v>
       </c>
       <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7920,7 +8410,6 @@
       <c r="Y48" t="b">
         <v>1</v>
       </c>
-      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="n">
         <v>0</v>
       </c>
@@ -7929,18 +8418,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="n">
         <v>1</v>
       </c>
@@ -7970,6 +8447,27 @@
       </c>
       <c r="AX48" t="n">
         <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -8068,7 +8566,6 @@
       <c r="Y49" t="b">
         <v>0</v>
       </c>
-      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="n">
         <v>1</v>
       </c>
@@ -8077,18 +8574,6 @@
           <t>[{"span_text": "me degoute", "mode": "Désignée", "categorie": "Dégoût", "categorie2": null, "justification": "Le terme 'dégoûte' est un mot du lexique émotionnel qui nomme explicitement l'émotion de dégoût."}]</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
@@ -8117,6 +8602,27 @@
         <v>0</v>
       </c>
       <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8216,7 +8722,6 @@
       <c r="Y50" t="b">
         <v>1</v>
       </c>
-      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="n">
         <v>2</v>
       </c>
@@ -8235,8 +8740,6 @@
           <t>bande de chienne</t>
         </is>
       </c>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -8247,8 +8750,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -8259,8 +8760,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
@@ -8290,6 +8789,27 @@
       </c>
       <c r="AX50" t="n">
         <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -8388,7 +8908,6 @@
       <c r="Y51" t="b">
         <v>1</v>
       </c>
-      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
         <v>0</v>
       </c>
@@ -8397,18 +8916,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
@@ -8437,6 +8944,27 @@
         <v>0</v>
       </c>
       <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8536,7 +9064,6 @@
       <c r="Y52" t="b">
         <v>1</v>
       </c>
-      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="n">
         <v>1</v>
       </c>
@@ -8550,25 +9077,16 @@
           <t>ça se voit vous êtes pas des potes si ça vous est jamais de réconforter votre pote</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
@@ -8597,6 +9115,27 @@
         <v>0</v>
       </c>
       <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8709,18 +9248,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="n">
         <v>2</v>
       </c>
@@ -8749,6 +9276,27 @@
         <v>0</v>
       </c>
       <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8848,7 +9396,6 @@
       <c r="Y54" t="b">
         <v>0</v>
       </c>
-      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="n">
         <v>1</v>
       </c>
@@ -8857,18 +9404,6 @@
           <t>[{"span_text": "ftg", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'abréviation 'ftg' (ferme ta gueule) est une injonction agressive qui exprime de la colère via une marque lexicale à forte charge affective négative."}]</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
@@ -8897,6 +9432,27 @@
         <v>0</v>
       </c>
       <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8996,7 +9552,6 @@
       <c r="Y55" t="b">
         <v>1</v>
       </c>
-      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="n">
         <v>1</v>
       </c>
@@ -9010,25 +9565,16 @@
           <t>tais-toi et laisse-nous vivre</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="n">
         <v>1</v>
       </c>
@@ -9057,6 +9603,27 @@
         <v>0</v>
       </c>
       <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9156,7 +9723,6 @@
       <c r="Y56" t="b">
         <v>1</v>
       </c>
-      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="n">
         <v>0</v>
       </c>
@@ -9165,18 +9731,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="n">
         <v>1</v>
       </c>
@@ -9205,6 +9759,27 @@
         <v>0</v>
       </c>
       <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9304,7 +9879,6 @@
       <c r="Y57" t="b">
         <v>1</v>
       </c>
-      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="n">
         <v>0</v>
       </c>
@@ -9313,18 +9887,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
       <c r="AO57" t="n">
         <v>1</v>
       </c>
@@ -9353,6 +9915,27 @@
         <v>0</v>
       </c>
       <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9452,7 +10035,6 @@
       <c r="Y58" t="b">
         <v>1</v>
       </c>
-      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="n">
         <v>0</v>
       </c>
@@ -9461,18 +10043,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
       <c r="AO58" t="n">
         <v>1</v>
       </c>
@@ -9501,6 +10071,27 @@
         <v>0</v>
       </c>
       <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9600,7 +10191,6 @@
       <c r="Y59" t="b">
         <v>1</v>
       </c>
-      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="n">
         <v>0</v>
       </c>
@@ -9609,18 +10199,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
       <c r="AO59" t="n">
         <v>2</v>
       </c>
@@ -9649,6 +10227,27 @@
         <v>0</v>
       </c>
       <c r="AX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9748,7 +10347,6 @@
       <c r="Y60" t="b">
         <v>0</v>
       </c>
-      <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="n">
         <v>1</v>
       </c>
@@ -9757,18 +10355,6 @@
           <t>[{"span_text": "c'est quoi le rapport entre être gouine et être une pute ?", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "La question rhétorique exprime une indignation face à l'amalgame homophobe formulé par l'harceleur."}]</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
       <c r="AO60" t="n">
         <v>0</v>
       </c>
@@ -9797,6 +10383,27 @@
         <v>0</v>
       </c>
       <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9896,7 +10503,6 @@
       <c r="Y61" t="b">
         <v>1</v>
       </c>
-      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="n">
         <v>0</v>
       </c>
@@ -9905,18 +10511,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="n">
         <v>1</v>
       </c>
@@ -9945,6 +10539,27 @@
         <v>0</v>
       </c>
       <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10044,7 +10659,6 @@
       <c r="Y62" t="b">
         <v>1</v>
       </c>
-      <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="n">
         <v>2</v>
       </c>
@@ -10063,8 +10677,6 @@
           <t>gouine</t>
         </is>
       </c>
-      <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -10075,8 +10687,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -10087,8 +10697,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="n">
         <v>1</v>
       </c>
@@ -10117,6 +10725,27 @@
         <v>0</v>
       </c>
       <c r="AX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10216,7 +10845,6 @@
       <c r="Y63" t="b">
         <v>1</v>
       </c>
-      <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="n">
         <v>0</v>
       </c>
@@ -10225,18 +10853,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
       <c r="AO63" t="n">
         <v>0</v>
       </c>
@@ -10265,6 +10881,27 @@
         <v>0</v>
       </c>
       <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10364,7 +11001,6 @@
       <c r="Y64" t="b">
         <v>0</v>
       </c>
-      <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="n">
         <v>1</v>
       </c>
@@ -10373,18 +11009,6 @@
           <t>[{"span_text": "ftg", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'abréviation 'ftg' (ferme ta gueule) est une injonction agressive qui exprime de la colère envers la victime."}]</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr"/>
-      <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr"/>
       <c r="AO64" t="n">
         <v>0</v>
       </c>
@@ -10413,6 +11037,27 @@
         <v>0</v>
       </c>
       <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10512,7 +11157,6 @@
       <c r="Y65" t="b">
         <v>1</v>
       </c>
-      <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="n">
         <v>0</v>
       </c>
@@ -10521,18 +11165,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr"/>
       <c r="AO65" t="n">
         <v>1</v>
       </c>
@@ -10561,6 +11193,27 @@
         <v>0</v>
       </c>
       <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10660,7 +11313,6 @@
       <c r="Y66" t="b">
         <v>0</v>
       </c>
-      <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="n">
         <v>2</v>
       </c>
@@ -10669,18 +11321,6 @@
           <t>[{"span_text": "grave", "mode": "Montrée", "categorie": "Dégoût", "categorie2": null, "justification": "Terme argotique d'intensification qui renforce l'expression du dégoût et marque l'adhésion forte à l'énoncé précédent."}, {"span_text": "vous me degouter", "mode": "Désignée", "categorie": "Dégoût", "categorie2": null, "justification": "Le verbe 'dégoûter' est un terme du lexique émotionnel qui nomme explicitement l'émotion de dégoût ressentie par l'auteur."}]</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
@@ -10709,6 +11349,27 @@
         <v>0</v>
       </c>
       <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10808,7 +11469,6 @@
       <c r="Y67" t="b">
         <v>1</v>
       </c>
-      <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="n">
         <v>0</v>
       </c>
@@ -10817,18 +11477,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr"/>
-      <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
-      <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="inlineStr"/>
-      <c r="AN67" t="inlineStr"/>
       <c r="AO67" t="n">
         <v>1</v>
       </c>
@@ -10857,6 +11505,27 @@
         <v>0</v>
       </c>
       <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10956,7 +11625,6 @@
       <c r="Y68" t="b">
         <v>1</v>
       </c>
-      <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="n">
         <v>0</v>
       </c>
@@ -10965,18 +11633,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr"/>
-      <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
-      <c r="AN68" t="inlineStr"/>
       <c r="AO68" t="n">
         <v>1</v>
       </c>
@@ -11005,6 +11661,27 @@
         <v>0</v>
       </c>
       <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11104,7 +11781,6 @@
       <c r="Y69" t="b">
         <v>1</v>
       </c>
-      <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="n">
         <v>1</v>
       </c>
@@ -11118,25 +11794,16 @@
           <t>grosse pute</t>
         </is>
       </c>
-      <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
-      <c r="AN69" t="inlineStr"/>
       <c r="AO69" t="n">
         <v>1</v>
       </c>
@@ -11165,6 +11832,27 @@
         <v>0</v>
       </c>
       <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11264,7 +11952,6 @@
       <c r="Y70" t="b">
         <v>1</v>
       </c>
-      <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="n">
         <v>0</v>
       </c>
@@ -11273,18 +11960,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr"/>
-      <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
-      <c r="AN70" t="inlineStr"/>
       <c r="AO70" t="n">
         <v>2</v>
       </c>
@@ -11313,6 +11988,27 @@
         <v>0</v>
       </c>
       <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11412,7 +12108,6 @@
       <c r="Y71" t="b">
         <v>0</v>
       </c>
-      <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="n">
         <v>5</v>
       </c>
@@ -11421,18 +12116,6 @@
           <t>[{"span_text": "ftg", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "Abréviation argotique 'ferme ta gueule' exprimant une hostilité agressive envers l'interlocuteur."}, {"span_text": "gouine", "mode": "Montrée", "categorie": "Colère", "categorie2": "Dégoût", "justification": "Insulte homophobe à forte charge affective négative révélant colère et dégoût de l'auteur."}, {"span_text": "sombre pute", "mode": "Montrée", "categorie": "Colère", "categorie2": "Dégoût", "justification": "Insulte péjorative à forte connotation négative exprimant mépris et hostilité agressive."}, {"span_text": "gouine", "mode": "Montrée", "categorie": "Colère", "categorie2": "Dégoût", "justification": "Insulte homophobe à forte charge affective négative révélant colère et dégoût de l'auteur."}, {"span_text": "sombre pute", "mode": "Montrée", "categorie": "Colère", "categorie2": "Dégoût", "justification": "Insulte péjorative à forte connotation négative exprimant mépris et hostilité agressive."}]</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
-      <c r="AN71" t="inlineStr"/>
       <c r="AO71" t="n">
         <v>0</v>
       </c>
@@ -11462,6 +12145,27 @@
       </c>
       <c r="AX71" t="n">
         <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -11560,7 +12264,6 @@
       <c r="Y72" t="b">
         <v>1</v>
       </c>
-      <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="n">
         <v>1</v>
       </c>
@@ -11574,25 +12277,16 @@
           <t>on va dire a un gadjo de la violer sa va lui remettre les idée en place</t>
         </is>
       </c>
-      <c r="AD72" t="inlineStr"/>
-      <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr"/>
-      <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
-      <c r="AN72" t="inlineStr"/>
       <c r="AO72" t="n">
         <v>2</v>
       </c>
@@ -11621,6 +12315,27 @@
         <v>0</v>
       </c>
       <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11720,7 +12435,6 @@
       <c r="Y73" t="b">
         <v>1</v>
       </c>
-      <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="n">
         <v>0</v>
       </c>
@@ -11729,18 +12443,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="inlineStr"/>
-      <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr"/>
-      <c r="AJ73" t="inlineStr"/>
-      <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
-      <c r="AN73" t="inlineStr"/>
       <c r="AO73" t="n">
         <v>2</v>
       </c>
@@ -11769,6 +12471,27 @@
         <v>0</v>
       </c>
       <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11868,7 +12591,6 @@
       <c r="Y74" t="b">
         <v>1</v>
       </c>
-      <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="n">
         <v>0</v>
       </c>
@@ -11877,18 +12599,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
-      <c r="AK74" t="inlineStr"/>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr"/>
-      <c r="AN74" t="inlineStr"/>
       <c r="AO74" t="n">
         <v>1</v>
       </c>
@@ -11917,6 +12627,27 @@
         <v>0</v>
       </c>
       <c r="AX74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12029,18 +12760,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr"/>
-      <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="inlineStr"/>
       <c r="AO75" t="n">
         <v>0</v>
       </c>
@@ -12069,6 +12788,27 @@
         <v>0</v>
       </c>
       <c r="AX75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12181,18 +12921,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr"/>
-      <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="inlineStr"/>
-      <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
-      <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr"/>
-      <c r="AN76" t="inlineStr"/>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
@@ -12221,6 +12949,27 @@
         <v>0</v>
       </c>
       <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12320,7 +13069,6 @@
       <c r="Y77" t="b">
         <v>1</v>
       </c>
-      <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="n">
         <v>0</v>
       </c>
@@ -12329,18 +13077,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr"/>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
-      <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="inlineStr"/>
       <c r="AO77" t="n">
         <v>1</v>
       </c>
@@ -12369,6 +13105,27 @@
         <v>0</v>
       </c>
       <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12468,7 +13225,6 @@
       <c r="Y78" t="b">
         <v>1</v>
       </c>
-      <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="n">
         <v>0</v>
       </c>
@@ -12477,18 +13233,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr"/>
-      <c r="AN78" t="inlineStr"/>
       <c r="AO78" t="n">
         <v>1</v>
       </c>
@@ -12517,6 +13261,27 @@
         <v>0</v>
       </c>
       <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12616,7 +13381,6 @@
       <c r="Y79" t="b">
         <v>1</v>
       </c>
-      <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="n">
         <v>1</v>
       </c>
@@ -12630,25 +13394,16 @@
           <t>t'as des problèmes</t>
         </is>
       </c>
-      <c r="AD79" t="inlineStr"/>
-      <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
-      <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
-      <c r="AN79" t="inlineStr"/>
       <c r="AO79" t="n">
         <v>1</v>
       </c>
@@ -12677,6 +13432,27 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12789,18 +13565,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
-      <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
-      <c r="AN80" t="inlineStr"/>
       <c r="AO80" t="n">
         <v>2</v>
       </c>
@@ -12829,6 +13593,27 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12928,7 +13713,6 @@
       <c r="Y81" t="b">
         <v>1</v>
       </c>
-      <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="n">
         <v>1</v>
       </c>
@@ -12942,25 +13726,16 @@
           <t>tu te rends compte de ce que tu dis là ??</t>
         </is>
       </c>
-      <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
-      <c r="AN81" t="inlineStr"/>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
@@ -12989,6 +13764,27 @@
         <v>0</v>
       </c>
       <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13088,7 +13884,6 @@
       <c r="Y82" t="b">
         <v>1</v>
       </c>
-      <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="n">
         <v>0</v>
       </c>
@@ -13097,18 +13892,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr"/>
-      <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="n">
         <v>3</v>
       </c>
@@ -13138,6 +13921,27 @@
       </c>
       <c r="AX82" t="n">
         <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -13236,7 +14040,6 @@
       <c r="Y83" t="b">
         <v>1</v>
       </c>
-      <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="n">
         <v>1</v>
       </c>
@@ -13250,25 +14053,16 @@
           <t>ftg</t>
         </is>
       </c>
-      <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr"/>
-      <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="n">
         <v>1</v>
       </c>
@@ -13297,6 +14091,27 @@
         <v>0</v>
       </c>
       <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,7 +14211,6 @@
       <c r="Y84" t="b">
         <v>1</v>
       </c>
-      <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="n">
         <v>0</v>
       </c>
@@ -13405,18 +14219,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr"/>
-      <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="inlineStr"/>
-      <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
-      <c r="AJ84" t="inlineStr"/>
-      <c r="AK84" t="inlineStr"/>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="inlineStr"/>
-      <c r="AN84" t="inlineStr"/>
       <c r="AO84" t="n">
         <v>0</v>
       </c>
@@ -13445,6 +14247,27 @@
         <v>0</v>
       </c>
       <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13544,7 +14367,6 @@
       <c r="Y85" t="b">
         <v>1</v>
       </c>
-      <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="n">
         <v>3</v>
       </c>
@@ -13568,7 +14390,6 @@
           <t>ptdrrr</t>
         </is>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -13584,7 +14405,6 @@
           <t>Joie</t>
         </is>
       </c>
-      <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr">
         <is>
           <t>Suggérée</t>
@@ -13600,7 +14420,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr"/>
       <c r="AO85" t="n">
         <v>1</v>
       </c>
@@ -13630,6 +14449,27 @@
       </c>
       <c r="AX85" t="n">
         <v>1</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -13728,7 +14568,6 @@
       <c r="Y86" t="b">
         <v>1</v>
       </c>
-      <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="n">
         <v>3</v>
       </c>
@@ -13752,7 +14591,6 @@
           <t>personne ne mérite ca</t>
         </is>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -13768,7 +14606,6 @@
           <t>Tristesse</t>
         </is>
       </c>
-      <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -13784,7 +14621,6 @@
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr"/>
       <c r="AO86" t="n">
         <v>1</v>
       </c>
@@ -13813,6 +14649,27 @@
         <v>0</v>
       </c>
       <c r="AX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13912,7 +14769,6 @@
       <c r="Y87" t="b">
         <v>1</v>
       </c>
-      <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="n">
         <v>0</v>
       </c>
@@ -13921,18 +14777,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr"/>
-      <c r="AD87" t="inlineStr"/>
-      <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="inlineStr"/>
-      <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
-      <c r="AJ87" t="inlineStr"/>
-      <c r="AK87" t="inlineStr"/>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="inlineStr"/>
-      <c r="AN87" t="inlineStr"/>
       <c r="AO87" t="n">
         <v>1</v>
       </c>
@@ -13961,6 +14805,27 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14060,7 +14925,6 @@
       <c r="Y88" t="b">
         <v>1</v>
       </c>
-      <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="n">
         <v>0</v>
       </c>
@@ -14069,18 +14933,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr"/>
-      <c r="AD88" t="inlineStr"/>
-      <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr"/>
-      <c r="AG88" t="inlineStr"/>
-      <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr"/>
-      <c r="AJ88" t="inlineStr"/>
-      <c r="AK88" t="inlineStr"/>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="inlineStr"/>
-      <c r="AN88" t="inlineStr"/>
       <c r="AO88" t="n">
         <v>2</v>
       </c>
@@ -14110,6 +14962,27 @@
       </c>
       <c r="AX88" t="n">
         <v>0</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -14208,7 +15081,6 @@
       <c r="Y89" t="b">
         <v>0</v>
       </c>
-      <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="n">
         <v>3</v>
       </c>
@@ -14217,18 +15089,6 @@
           <t>[{"span_text": "allo le viol c'est pas une blague", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'interpellation directe 'allo' et la dénonciation indignée de la minimisation du viol expriment une colère/indignation forte."}, {"span_text": "grosse bouffonne", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'insulte à forte charge péjorative exprime la colère et le mépris de l'auteure envers son interlocutrice."}, {"span_text": "va falloir avoir des valeurs un peu là un minimum", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "Le ton impératif et l'injonction morale ('va falloir') traduisent une indignation et une colère face au manque de valeurs perçu."}]</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
-      <c r="AN89" t="inlineStr"/>
       <c r="AO89" t="n">
         <v>0</v>
       </c>
@@ -14258,6 +15118,27 @@
       </c>
       <c r="AX89" t="n">
         <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -14356,7 +15237,6 @@
       <c r="Y90" t="b">
         <v>0</v>
       </c>
-      <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="n">
         <v>2</v>
       </c>
@@ -14365,18 +15245,6 @@
           <t>[{"span_text": "laissé la tranquille", "mode": "Comportementale", "categorie": "Colère", "categorie2": null, "justification": "L'injonction à laisser quelqu'un tranquille est une attitude discursive de protestation/défense qui exprime de l'indignation."}, {"span_text": "elle a le droit d'aimer qui elle veut", "mode": "Suggérée", "categorie": "Colère", "categorie2": null, "justification": "Défendre le droit d'une personne à aimer librement face à une attaque homophobe est prototypiquement associé à l'indignation/colère contre l'injustice."}]</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr"/>
-      <c r="AD90" t="inlineStr"/>
-      <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
-      <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
-      <c r="AK90" t="inlineStr"/>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="inlineStr"/>
-      <c r="AN90" t="inlineStr"/>
       <c r="AO90" t="n">
         <v>0</v>
       </c>
@@ -14405,6 +15273,27 @@
         <v>0</v>
       </c>
       <c r="AX90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14504,7 +15393,6 @@
       <c r="Y91" t="b">
         <v>1</v>
       </c>
-      <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="n">
         <v>1</v>
       </c>
@@ -14518,25 +15406,16 @@
           <t>c une blague</t>
         </is>
       </c>
-      <c r="AD91" t="inlineStr"/>
-      <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="inlineStr"/>
-      <c r="AN91" t="inlineStr"/>
       <c r="AO91" t="n">
         <v>1</v>
       </c>
@@ -14565,6 +15444,27 @@
         <v>0</v>
       </c>
       <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14664,7 +15564,6 @@
       <c r="Y92" t="b">
         <v>1</v>
       </c>
-      <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="n">
         <v>2</v>
       </c>
@@ -14683,8 +15582,6 @@
           <t>que des traitres</t>
         </is>
       </c>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -14695,8 +15592,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AI92" t="inlineStr"/>
-      <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -14707,8 +15602,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr"/>
-      <c r="AN92" t="inlineStr"/>
       <c r="AO92" t="n">
         <v>1</v>
       </c>
@@ -14738,6 +15631,27 @@
       </c>
       <c r="AX92" t="n">
         <v>0</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -14836,7 +15750,6 @@
       <c r="Y93" t="b">
         <v>1</v>
       </c>
-      <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="n">
         <v>0</v>
       </c>
@@ -14845,18 +15758,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr"/>
-      <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
-      <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
-      <c r="AK93" t="inlineStr"/>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="inlineStr"/>
-      <c r="AN93" t="inlineStr"/>
       <c r="AO93" t="n">
         <v>1</v>
       </c>
@@ -14885,6 +15786,27 @@
         <v>0</v>
       </c>
       <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14984,7 +15906,6 @@
       <c r="Y94" t="b">
         <v>1</v>
       </c>
-      <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="n">
         <v>1</v>
       </c>
@@ -14998,25 +15919,16 @@
           <t>si vous ne disiez pas n'importe quoi aussi,  les gens seraient peut-êtr eun peu avec vous</t>
         </is>
       </c>
-      <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AL94" t="inlineStr"/>
-      <c r="AM94" t="inlineStr"/>
-      <c r="AN94" t="inlineStr"/>
       <c r="AO94" t="n">
         <v>0</v>
       </c>
@@ -15045,6 +15957,27 @@
         <v>0</v>
       </c>
       <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15144,7 +16077,6 @@
       <c r="Y95" t="b">
         <v>1</v>
       </c>
-      <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="n">
         <v>2</v>
       </c>
@@ -15163,8 +16095,6 @@
           <t>mais la blague</t>
         </is>
       </c>
-      <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr">
         <is>
           <t>Joie</t>
@@ -15175,8 +16105,6 @@
           <t>Joie</t>
         </is>
       </c>
-      <c r="AI95" t="inlineStr"/>
-      <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -15187,8 +16115,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr"/>
-      <c r="AN95" t="inlineStr"/>
       <c r="AO95" t="n">
         <v>2</v>
       </c>
@@ -15217,6 +16143,27 @@
         <v>0</v>
       </c>
       <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15316,7 +16263,6 @@
       <c r="Y96" t="b">
         <v>1</v>
       </c>
-      <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="n">
         <v>4</v>
       </c>
@@ -15413,6 +16359,27 @@
         <v>0</v>
       </c>
       <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15512,7 +16479,6 @@
       <c r="Y97" t="b">
         <v>1</v>
       </c>
-      <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="n">
         <v>3</v>
       </c>
@@ -15536,7 +16502,6 @@
           <t>bande de crasseux</t>
         </is>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -15552,7 +16517,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -15568,7 +16532,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr"/>
       <c r="AO97" t="n">
         <v>1</v>
       </c>
@@ -15597,6 +16560,27 @@
         <v>0</v>
       </c>
       <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15696,7 +16680,6 @@
       <c r="Y98" t="b">
         <v>0</v>
       </c>
-      <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="n">
         <v>2</v>
       </c>
@@ -15705,18 +16688,6 @@
           <t>[{"span_text": "vous allez trop loin", "mode": "Suggérée", "categorie": "Colère", "categorie2": null, "justification": "Dénoncer que quelqu'un 'va trop loin' est prototypiquement associé à une réaction d'indignation/colère face à un comportement excessif."}, {"span_text": "vous méritez les deux connasses", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'insulte 'connasses' est un terme péjoratif à forte charge affective qui exprime la colère de l'auteure."}]</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr"/>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98" t="inlineStr"/>
-      <c r="AN98" t="inlineStr"/>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
@@ -15745,6 +16716,27 @@
         <v>0</v>
       </c>
       <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15844,7 +16836,6 @@
       <c r="Y99" t="b">
         <v>0</v>
       </c>
-      <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="n">
         <v>1</v>
       </c>
@@ -15853,18 +16844,6 @@
           <t>[{"span_text": "merde", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'interjection 'merde' est un marqueur lexical à forte charge affective exprimant l'irritation ou l'agacement de l'auteur."}]</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
-      <c r="AJ99" t="inlineStr"/>
-      <c r="AK99" t="inlineStr"/>
-      <c r="AL99" t="inlineStr"/>
-      <c r="AM99" t="inlineStr"/>
-      <c r="AN99" t="inlineStr"/>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
@@ -15894,6 +16873,27 @@
       </c>
       <c r="AX99" t="n">
         <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -15992,7 +16992,6 @@
       <c r="Y100" t="b">
         <v>0</v>
       </c>
-      <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="n">
         <v>2</v>
       </c>
@@ -16001,18 +17000,6 @@
           <t>[{"span_text": "STOP LESBIENNES !!!!", "mode": "Montrée", "categorie": "Colère", "categorie2": "Dégoût", "justification": "L'usage des majuscules, du terme homophobe 'LESBIENNES' comme insulte rejetante, et des points d'exclamation multiples révèlent une colère agressive teintée de dégoût envers les personnes visées."}, {"span_text": "STOP LESBIENNES !!!!", "mode": "Montrée", "categorie": "Colère", "categorie2": "Dégoût", "justification": "L'usage des majuscules, du terme homophobe 'LESBIENNES' comme insulte rejetante, et des points d'exclamation multiples révèlent une colère agressive teintée de dégoût envers les personnes visées."}]</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
-      <c r="AK100" t="inlineStr"/>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="inlineStr"/>
-      <c r="AN100" t="inlineStr"/>
       <c r="AO100" t="n">
         <v>0</v>
       </c>
@@ -16041,6 +17028,27 @@
         <v>0</v>
       </c>
       <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16140,7 +17148,6 @@
       <c r="Y101" t="b">
         <v>0</v>
       </c>
-      <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="n">
         <v>1</v>
       </c>
@@ -16149,18 +17156,6 @@
           <t>[{"span_text": "DEHORSSSSS", "mode": "Montrée", "categorie": "Colère", "categorie2": null, "justification": "L'injonction en majuscules avec étirement graphique exprime une hostilité agressive et une indignation caractéristiques de la colère."}]</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr"/>
-      <c r="AD101" t="inlineStr"/>
-      <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
-      <c r="AK101" t="inlineStr"/>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="inlineStr"/>
-      <c r="AN101" t="inlineStr"/>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
@@ -16189,6 +17184,27 @@
         <v>0</v>
       </c>
       <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16288,7 +17304,6 @@
       <c r="Y102" t="b">
         <v>1</v>
       </c>
-      <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="n">
         <v>0</v>
       </c>
@@ -16297,18 +17312,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr"/>
-      <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr"/>
-      <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
-      <c r="AJ102" t="inlineStr"/>
-      <c r="AK102" t="inlineStr"/>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="inlineStr"/>
-      <c r="AN102" t="inlineStr"/>
       <c r="AO102" t="n">
         <v>0</v>
       </c>
@@ -16337,6 +17340,27 @@
         <v>0</v>
       </c>
       <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16436,7 +17460,6 @@
       <c r="Y103" t="b">
         <v>1</v>
       </c>
-      <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="n">
         <v>0</v>
       </c>
@@ -16445,18 +17468,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr"/>
-      <c r="AD103" t="inlineStr"/>
-      <c r="AE103" t="inlineStr"/>
-      <c r="AF103" t="inlineStr"/>
-      <c r="AG103" t="inlineStr"/>
-      <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr"/>
-      <c r="AJ103" t="inlineStr"/>
-      <c r="AK103" t="inlineStr"/>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="inlineStr"/>
-      <c r="AN103" t="inlineStr"/>
       <c r="AO103" t="n">
         <v>0</v>
       </c>
@@ -16485,6 +17496,27 @@
         <v>0</v>
       </c>
       <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16584,7 +17616,6 @@
       <c r="Y104" t="b">
         <v>1</v>
       </c>
-      <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="n">
         <v>2</v>
       </c>
@@ -16603,8 +17634,6 @@
           <t>homophobes</t>
         </is>
       </c>
-      <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -16615,8 +17644,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AI104" t="inlineStr"/>
-      <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -16627,8 +17654,6 @@
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr"/>
-      <c r="AN104" t="inlineStr"/>
       <c r="AO104" t="n">
         <v>0</v>
       </c>
@@ -16657,6 +17682,27 @@
         <v>0</v>
       </c>
       <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE104" t="n">
         <v>0</v>
       </c>
     </row>
